--- a/data/trans_orig/IQ11_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ11_1-Habitat-trans_orig.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>65520</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28180</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -10410,12 +10410,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10865,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14578,12 +14578,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
